--- a/frontend/public/downloads/DiamondStats_Softball_Scorebook_Final.xlsx
+++ b/frontend/public/downloads/DiamondStats_Softball_Scorebook_Final.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmr03\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\my-app\DiamondStatsV1\frontend\public\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -75,9 +75,6 @@
     <t>E</t>
   </si>
   <si>
-    <t>HR Permitidos</t>
-  </si>
-  <si>
     <t>1B</t>
   </si>
   <si>
@@ -157,6 +154,9 @@
   </si>
   <si>
     <t>Notas / cambios / sustituciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HR </t>
   </si>
 </sst>
 </file>
@@ -238,31 +238,29 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFA6A6A6"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FFA6A6A6"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FFA6A6A6"/>
+        <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFA6A6A6"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF1E1E1E"/>
+      <left style="thick">
+        <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color rgb="FF1E1E1E"/>
+      <right style="thick">
+        <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color rgb="FF1E1E1E"/>
+      <top style="thick">
+        <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FF1E1E1E"/>
+      <bottom style="thick">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -270,61 +268,58 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2903,132 +2898,134 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="5" style="3" customWidth="1"/>
-    <col min="2" max="2" width="24" style="3" customWidth="1"/>
-    <col min="3" max="3" width="10" style="3" customWidth="1"/>
-    <col min="4" max="10" width="12" style="3" customWidth="1"/>
-    <col min="11" max="13" width="7" style="3" customWidth="1"/>
-    <col min="14" max="14" width="9" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="8.83984375" style="3"/>
+    <col min="1" max="1" width="5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10" style="1" customWidth="1"/>
+    <col min="4" max="10" width="12" style="1" customWidth="1"/>
+    <col min="11" max="13" width="7" style="1" customWidth="1"/>
+    <col min="14" max="14" width="9" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.83984375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
     </row>
     <row r="2" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="4" t="s">
+    <row r="3" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="4" spans="1:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A4" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="4" t="s">
+      <c r="B4" s="21"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="4" t="s">
+      <c r="F4" s="22"/>
+      <c r="G4" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="4" t="s">
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
+    <row r="5" spans="1:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="4" t="s">
+      <c r="B6" s="21"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
     </row>
-    <row r="8" spans="1:14" ht="26.05" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A8" s="8" t="s">
+    <row r="7" spans="1:14" ht="14.7" thickTop="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="8" spans="1:14" ht="26.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="K8" s="9" t="s">
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="K8" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A9" s="13" t="s">
         <v>9</v>
       </c>
@@ -3054,163 +3051,164 @@
         <v>16</v>
       </c>
       <c r="I9" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="K9" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="K9" s="10" t="s">
+      <c r="L9" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="L9" s="11" t="s">
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+    </row>
+    <row r="10" spans="1:14" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="K10" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
+      <c r="L10" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
     </row>
-    <row r="10" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="K10" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="L10" s="11" t="s">
+    <row r="11" spans="1:14" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="K11" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
+      <c r="L11" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
     </row>
-    <row r="11" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="K11" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L11" s="11" t="s">
+    <row r="12" spans="1:14" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="K12" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
+      <c r="L12" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
     </row>
-    <row r="12" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="K12" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L12" s="11" t="s">
+    <row r="13" spans="1:14" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="K13" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="L13" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
     </row>
-    <row r="13" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="K13" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="L13" s="11" t="s">
+    <row r="14" spans="1:14" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="K14" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="L14" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
     </row>
-    <row r="14" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="K14" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L14" s="11" t="s">
+    <row r="15" spans="1:14" ht="14.7" thickTop="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="17" spans="1:14" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="A17" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
     </row>
-    <row r="17" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A17" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-    </row>
-    <row r="18" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:14" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A18" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="D18" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="E18" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="F18" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="G18" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="13" t="s">
+      <c r="H18" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="13" t="s">
+      <c r="I18" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="I18" s="13" t="s">
+      <c r="J18" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="J18" s="13" t="s">
+      <c r="K18" s="13" t="s">
         <v>37</v>
-      </c>
-      <c r="K18" s="13" t="s">
-        <v>38</v>
       </c>
       <c r="L18" s="13" t="s">
         <v>14</v>
@@ -3219,381 +3217,396 @@
         <v>15</v>
       </c>
       <c r="N18" s="13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="46" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
+    </row>
+    <row r="20" spans="1:14" ht="46" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A20" s="15"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+    </row>
+    <row r="21" spans="1:14" ht="46" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+    </row>
+    <row r="22" spans="1:14" ht="46" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="15"/>
+    </row>
+    <row r="23" spans="1:14" ht="46" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
+      <c r="N23" s="14"/>
+    </row>
+    <row r="24" spans="1:14" ht="46" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="15"/>
+    </row>
+    <row r="25" spans="1:14" ht="46" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A25" s="14"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="14"/>
+      <c r="N25" s="14"/>
+    </row>
+    <row r="26" spans="1:14" ht="46" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A26" s="15"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+    </row>
+    <row r="27" spans="1:14" ht="46" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A27" s="14"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
+      <c r="N27" s="14"/>
+    </row>
+    <row r="28" spans="1:14" ht="46" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="15"/>
+    </row>
+    <row r="29" spans="1:14" ht="46" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A29" s="14"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
+    </row>
+    <row r="30" spans="1:14" ht="46" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="15"/>
+      <c r="N30" s="15"/>
+    </row>
+    <row r="31" spans="1:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="32" spans="1:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A32" s="6" t="s">
         <v>39</v>
       </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="9">
+        <v>1</v>
+      </c>
+      <c r="E32" s="9">
+        <v>2</v>
+      </c>
+      <c r="F32" s="9">
+        <v>3</v>
+      </c>
+      <c r="G32" s="9">
+        <v>4</v>
+      </c>
+      <c r="H32" s="9">
+        <v>5</v>
+      </c>
+      <c r="I32" s="9">
+        <v>6</v>
+      </c>
+      <c r="J32" s="9">
+        <v>7</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="M32" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="N32" s="9" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="19" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="12"/>
+    <row r="33" spans="1:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A33" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="12"/>
+      <c r="M33" s="12"/>
+      <c r="N33" s="12"/>
     </row>
-    <row r="20" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
+    <row r="34" spans="1:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A34" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="12"/>
+      <c r="N34" s="12"/>
     </row>
-    <row r="21" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="12"/>
+    <row r="35" spans="1:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A35" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="12"/>
+      <c r="M35" s="12"/>
+      <c r="N35" s="12"/>
     </row>
-    <row r="22" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
+    <row r="36" spans="1:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A36" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
+      <c r="M36" s="12"/>
+      <c r="N36" s="12"/>
     </row>
-    <row r="23" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12"/>
+    <row r="37" spans="1:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="38" spans="1:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A38" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="7"/>
     </row>
-    <row r="24" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
+    <row r="39" spans="1:14" ht="22" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A39" s="8"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="8"/>
+      <c r="N39" s="8"/>
     </row>
-    <row r="25" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12"/>
-      <c r="N25" s="12"/>
+    <row r="40" spans="1:14" ht="22" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="8"/>
+      <c r="M40" s="8"/>
+      <c r="N40" s="8"/>
     </row>
-    <row r="26" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="14"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
+    <row r="41" spans="1:14" ht="22" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A41" s="8"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="8"/>
+      <c r="N41" s="8"/>
     </row>
-    <row r="27" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-    </row>
-    <row r="28" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="14"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="14"/>
-    </row>
-    <row r="29" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
-    </row>
-    <row r="30" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="14"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="17">
-        <v>1</v>
-      </c>
-      <c r="E32" s="17">
-        <v>2</v>
-      </c>
-      <c r="F32" s="17">
-        <v>3</v>
-      </c>
-      <c r="G32" s="17">
-        <v>4</v>
-      </c>
-      <c r="H32" s="17">
-        <v>5</v>
-      </c>
-      <c r="I32" s="17">
-        <v>6</v>
-      </c>
-      <c r="J32" s="17">
-        <v>7</v>
-      </c>
-      <c r="K32" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="L32" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="M32" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="N32" s="17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="20"/>
-      <c r="K33" s="20"/>
-      <c r="L33" s="20"/>
-      <c r="M33" s="20"/>
-      <c r="N33" s="20"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
-      <c r="M34" s="20"/>
-      <c r="N34" s="20"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-      <c r="K35" s="20"/>
-      <c r="L35" s="20"/>
-      <c r="M35" s="20"/>
-      <c r="N35" s="20"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
-      <c r="J36" s="20"/>
-      <c r="K36" s="20"/>
-      <c r="L36" s="20"/>
-      <c r="M36" s="20"/>
-      <c r="N36" s="20"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="22"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="22"/>
-      <c r="J38" s="22"/>
-      <c r="K38" s="22"/>
-      <c r="L38" s="22"/>
-      <c r="M38" s="22"/>
-      <c r="N38" s="22"/>
-    </row>
-    <row r="39" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="23"/>
-      <c r="B39" s="23"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="23"/>
-      <c r="G39" s="23"/>
-      <c r="H39" s="23"/>
-      <c r="I39" s="23"/>
-      <c r="J39" s="23"/>
-      <c r="K39" s="23"/>
-      <c r="L39" s="23"/>
-      <c r="M39" s="23"/>
-      <c r="N39" s="23"/>
-    </row>
-    <row r="40" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="23"/>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="23"/>
-      <c r="J40" s="23"/>
-      <c r="K40" s="23"/>
-      <c r="L40" s="23"/>
-      <c r="M40" s="23"/>
-      <c r="N40" s="23"/>
-    </row>
-    <row r="41" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="23"/>
-      <c r="B41" s="23"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="23"/>
-      <c r="H41" s="23"/>
-      <c r="I41" s="23"/>
-      <c r="J41" s="23"/>
-      <c r="K41" s="23"/>
-      <c r="L41" s="23"/>
-      <c r="M41" s="23"/>
-      <c r="N41" s="23"/>
-    </row>
+    <row r="42" spans="1:14" ht="14.7" thickTop="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="F4"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G4"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="K4"/>
+    <mergeCell ref="C4:D4"/>
     <mergeCell ref="A1:N2"/>
     <mergeCell ref="A17:N17"/>
     <mergeCell ref="A36:C36"/>
@@ -3610,18 +3623,6 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="L10:N10"/>
-    <mergeCell ref="F4"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G4"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="K4"/>
-    <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.5" footer="0.5"/>
   <pageSetup scale="67" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/frontend/public/downloads/DiamondStats_Softball_Scorebook_Final.xlsx
+++ b/frontend/public/downloads/DiamondStats_Softball_Scorebook_Final.xlsx
@@ -250,16 +250,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thick">
+      <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thick">
+      <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thick">
+      <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thick">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -268,22 +268,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -296,30 +310,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2898,7 +2899,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -2911,65 +2912,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
     </row>
     <row r="2" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
+      <c r="A2" s="23"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
     </row>
     <row r="3" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="4" spans="1:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="20" t="s">
+    <row r="4" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="20" t="s">
+      <c r="B4" s="8"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="22"/>
-      <c r="G4" s="20" t="s">
+      <c r="F4" s="9"/>
+      <c r="G4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="20" t="s">
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
     </row>
-    <row r="5" spans="1:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2985,29 +2986,28 @@
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
     </row>
-    <row r="6" spans="1:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="20" t="s">
+    <row r="6" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="20" t="s">
+      <c r="B6" s="8"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="21"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
     </row>
-    <row r="7" spans="1:14" ht="14.7" thickTop="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="8" spans="1:14" ht="26.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="4"/>
@@ -3018,148 +3018,147 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
-      <c r="K8" s="16" t="s">
+      <c r="K8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
     </row>
-    <row r="9" spans="1:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="13" t="s">
+    <row r="9" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A9" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="K9" s="18" t="s">
+      <c r="K9" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="19" t="s">
+      <c r="L9" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
     </row>
-    <row r="10" spans="1:14" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="K10" s="18" t="s">
+    <row r="10" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="K10" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="L10" s="19" t="s">
+      <c r="L10" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
     </row>
-    <row r="11" spans="1:14" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="K11" s="18" t="s">
+    <row r="11" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="K11" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="L11" s="19" t="s">
+      <c r="L11" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
     </row>
-    <row r="12" spans="1:14" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="K12" s="18" t="s">
+    <row r="12" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="K12" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="L12" s="19" t="s">
+      <c r="L12" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
     </row>
-    <row r="13" spans="1:14" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="K13" s="18" t="s">
+    <row r="13" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A13" s="20"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="K13" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="L13" s="19" t="s">
+      <c r="L13" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
     </row>
-    <row r="14" spans="1:14" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="K14" s="18" t="s">
+    <row r="14" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="K14" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="L14" s="19" t="s">
+      <c r="L14" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M14" s="19"/>
-      <c r="N14" s="19"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
     </row>
-    <row r="15" spans="1:14" ht="14.7" thickTop="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="17" spans="1:14" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B17" s="4"/>
@@ -3176,437 +3175,424 @@
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
     </row>
-    <row r="18" spans="1:14" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A18" s="13" t="s">
+    <row r="18" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A18" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="F18" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="13" t="s">
+      <c r="G18" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H18" s="13" t="s">
+      <c r="H18" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="I18" s="13" t="s">
+      <c r="I18" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J18" s="13" t="s">
+      <c r="J18" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="K18" s="13" t="s">
+      <c r="K18" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="L18" s="13" t="s">
+      <c r="L18" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="M18" s="13" t="s">
+      <c r="M18" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="N18" s="13" t="s">
+      <c r="N18" s="10" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="46" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
+    <row r="19" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
     </row>
-    <row r="20" spans="1:14" ht="46" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="15"/>
+    <row r="20" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A20" s="21"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="21"/>
+      <c r="M20" s="21"/>
+      <c r="N20" s="21"/>
     </row>
-    <row r="21" spans="1:14" ht="46" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
+    <row r="21" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A21" s="20"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
     </row>
-    <row r="22" spans="1:14" ht="46" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="15"/>
+    <row r="22" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A22" s="21"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="21"/>
+      <c r="M22" s="21"/>
+      <c r="N22" s="21"/>
     </row>
-    <row r="23" spans="1:14" ht="46" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
+    <row r="23" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
     </row>
-    <row r="24" spans="1:14" ht="46" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A24" s="15"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="15"/>
+    <row r="24" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A24" s="21"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="21"/>
+      <c r="M24" s="21"/>
+      <c r="N24" s="21"/>
     </row>
-    <row r="25" spans="1:14" ht="46" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
+    <row r="25" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A25" s="20"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
     </row>
-    <row r="26" spans="1:14" ht="46" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A26" s="15"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15"/>
+    <row r="26" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="21"/>
+      <c r="M26" s="21"/>
+      <c r="N26" s="21"/>
     </row>
-    <row r="27" spans="1:14" ht="46" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A27" s="14"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="14"/>
+    <row r="27" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A27" s="20"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
     </row>
-    <row r="28" spans="1:14" ht="46" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="15"/>
+    <row r="28" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="21"/>
     </row>
-    <row r="29" spans="1:14" ht="46" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A29" s="14"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14"/>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="14"/>
+    <row r="29" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
     </row>
-    <row r="30" spans="1:14" ht="46" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A30" s="15"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-      <c r="N30" s="15"/>
+    <row r="30" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="21"/>
+      <c r="M30" s="21"/>
+      <c r="N30" s="21"/>
     </row>
-    <row r="31" spans="1:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="32" spans="1:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A32" s="6" t="s">
+    <row r="31" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="32" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A32" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="9">
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="15">
         <v>1</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="15">
         <v>2</v>
       </c>
-      <c r="F32" s="9">
+      <c r="F32" s="15">
         <v>3</v>
       </c>
-      <c r="G32" s="9">
+      <c r="G32" s="15">
         <v>4</v>
       </c>
-      <c r="H32" s="9">
+      <c r="H32" s="15">
         <v>5</v>
       </c>
-      <c r="I32" s="9">
+      <c r="I32" s="15">
         <v>6</v>
       </c>
-      <c r="J32" s="9">
+      <c r="J32" s="15">
         <v>7</v>
       </c>
-      <c r="K32" s="9" t="s">
+      <c r="K32" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="L32" s="9" t="s">
+      <c r="L32" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="M32" s="9" t="s">
+      <c r="M32" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="N32" s="9" t="s">
+      <c r="N32" s="15" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="10" t="s">
+    <row r="33" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A33" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="12"/>
-      <c r="N33" s="12"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
+      <c r="M33" s="18"/>
+      <c r="N33" s="18"/>
     </row>
-    <row r="34" spans="1:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A34" s="10" t="s">
+    <row r="34" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A34" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
-      <c r="M34" s="12"/>
-      <c r="N34" s="12"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
+      <c r="M34" s="18"/>
+      <c r="N34" s="18"/>
     </row>
-    <row r="35" spans="1:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A35" s="10" t="s">
+    <row r="35" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A35" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
-      <c r="M35" s="12"/>
-      <c r="N35" s="12"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
+      <c r="M35" s="18"/>
+      <c r="N35" s="18"/>
     </row>
-    <row r="36" spans="1:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A36" s="10" t="s">
+    <row r="36" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A36" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="12"/>
-      <c r="L36" s="12"/>
-      <c r="M36" s="12"/>
-      <c r="N36" s="12"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
+      <c r="M36" s="18"/>
+      <c r="N36" s="18"/>
     </row>
-    <row r="37" spans="1:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="38" spans="1:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A38" s="6" t="s">
+    <row r="37" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="38" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A38" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="14"/>
+      <c r="L38" s="14"/>
+      <c r="M38" s="14"/>
+      <c r="N38" s="14"/>
     </row>
-    <row r="39" spans="1:14" ht="22" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
-      <c r="I39" s="8"/>
-      <c r="J39" s="8"/>
-      <c r="K39" s="8"/>
-      <c r="L39" s="8"/>
-      <c r="M39" s="8"/>
-      <c r="N39" s="8"/>
+    <row r="39" spans="1:14" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A39" s="19"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
     </row>
-    <row r="40" spans="1:14" ht="22" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A40" s="8"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
-      <c r="I40" s="8"/>
-      <c r="J40" s="8"/>
-      <c r="K40" s="8"/>
-      <c r="L40" s="8"/>
-      <c r="M40" s="8"/>
-      <c r="N40" s="8"/>
+    <row r="40" spans="1:14" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A40" s="19"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
     </row>
-    <row r="41" spans="1:14" ht="22" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
-      <c r="I41" s="8"/>
-      <c r="J41" s="8"/>
-      <c r="K41" s="8"/>
-      <c r="L41" s="8"/>
-      <c r="M41" s="8"/>
-      <c r="N41" s="8"/>
+    <row r="41" spans="1:14" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A41" s="19"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="19"/>
+      <c r="N41" s="19"/>
     </row>
-    <row r="42" spans="1:14" ht="14.7" thickTop="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="F4"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G4"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="K4"/>
-    <mergeCell ref="C4:D4"/>
     <mergeCell ref="A1:N2"/>
     <mergeCell ref="A17:N17"/>
     <mergeCell ref="A36:C36"/>
@@ -3623,6 +3609,18 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="L10:N10"/>
+    <mergeCell ref="F4"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G4"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="K4"/>
+    <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.5" footer="0.5"/>
   <pageSetup scale="67" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/frontend/public/downloads/DiamondStats_Softball_Scorebook_Final.xlsx
+++ b/frontend/public/downloads/DiamondStats_Softball_Scorebook_Final.xlsx
@@ -228,7 +228,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -264,18 +264,205 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashDotDot">
+        <color indexed="64"/>
+      </left>
+      <right style="dashDotDot">
+        <color indexed="64"/>
+      </right>
+      <top style="dashDotDot">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dashDotDot">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dashDotDot">
+        <color indexed="64"/>
+      </right>
+      <top style="dashDotDot">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dashDotDot">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="dashDotDot">
+        <color indexed="64"/>
+      </right>
+      <top style="dashDotDot">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dashDotDot">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashDotDot">
+        <color indexed="64"/>
+      </left>
+      <right style="dashDotDot">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="dashDotDot">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashDotDot">
+        <color indexed="64"/>
+      </left>
+      <right style="dashDotDot">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dashDotDot">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashDotDot">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="dashDotDot">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dashDotDot">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="dashDotDot">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dashDotDot">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashDotDot">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="dashDotDot">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dashDotDot">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -284,43 +471,51 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2912,63 +3107,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
     </row>
     <row r="2" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="23"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23"/>
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
     </row>
     <row r="3" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
     <row r="4" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="7" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="7" t="s">
+      <c r="F4" s="34"/>
+      <c r="G4" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="7" t="s">
+      <c r="H4" s="30"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
     </row>
     <row r="5" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A5" s="2"/>
@@ -2987,612 +3182,624 @@
       <c r="N5" s="2"/>
     </row>
     <row r="6" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="7" t="s">
+      <c r="B6" s="25"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="8"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
     </row>
     <row r="8" spans="1:14" ht="26.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="K8" s="5" t="s">
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="K8" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
     </row>
     <row r="9" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="12" t="s">
+      <c r="L9" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
     </row>
     <row r="10" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="20"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="K10" s="11" t="s">
+      <c r="A10" s="32"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
+      <c r="K10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L10" s="12" t="s">
+      <c r="L10" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
     </row>
     <row r="11" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="20"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="K11" s="11" t="s">
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="K11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="L11" s="12" t="s">
+      <c r="L11" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
     </row>
     <row r="12" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="20"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="K12" s="11" t="s">
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="K12" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="L12" s="12" t="s">
+      <c r="L12" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
     </row>
     <row r="13" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="20"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="K13" s="11" t="s">
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="K13" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="L13" s="12" t="s">
+      <c r="L13" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
     </row>
     <row r="14" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="20"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="K14" s="11" t="s">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="K14" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="L14" s="12" t="s">
+      <c r="L14" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
     </row>
     <row r="17" spans="1:14" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
     </row>
     <row r="18" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="H18" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I18" s="10" t="s">
+      <c r="I18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="J18" s="10" t="s">
+      <c r="J18" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="K18" s="10" t="s">
+      <c r="K18" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="L18" s="10" t="s">
+      <c r="L18" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="M18" s="10" t="s">
+      <c r="M18" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="N18" s="10" t="s">
+      <c r="N18" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A19" s="20"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="20"/>
-      <c r="N19" s="20"/>
+    <row r="19" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="31"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="31"/>
+      <c r="N19" s="31"/>
     </row>
-    <row r="20" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A20" s="21"/>
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
-      <c r="M20" s="21"/>
-      <c r="N20" s="21"/>
+    <row r="20" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="20"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
     </row>
-    <row r="21" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A21" s="20"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
+    <row r="21" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
     </row>
-    <row r="22" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="21"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
-      <c r="M22" s="21"/>
-      <c r="N22" s="21"/>
+    <row r="22" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
     </row>
-    <row r="23" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
+    <row r="23" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
     </row>
-    <row r="24" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A24" s="21"/>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="21"/>
-      <c r="K24" s="21"/>
-      <c r="L24" s="21"/>
-      <c r="M24" s="21"/>
-      <c r="N24" s="21"/>
+    <row r="24" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="20"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
     </row>
-    <row r="25" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A25" s="20"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
+    <row r="25" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
     </row>
-    <row r="26" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A26" s="21"/>
-      <c r="B26" s="21"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="21"/>
-      <c r="K26" s="21"/>
-      <c r="L26" s="21"/>
-      <c r="M26" s="21"/>
-      <c r="N26" s="21"/>
+    <row r="26" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="20"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
     </row>
-    <row r="27" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A27" s="20"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
-      <c r="M27" s="20"/>
-      <c r="N27" s="20"/>
+    <row r="27" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
     </row>
-    <row r="28" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A28" s="21"/>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
-      <c r="M28" s="21"/>
-      <c r="N28" s="21"/>
+    <row r="28" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="20"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
     </row>
-    <row r="29" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A29" s="20"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
-      <c r="M29" s="20"/>
-      <c r="N29" s="20"/>
+    <row r="29" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
     </row>
-    <row r="30" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A30" s="21"/>
-      <c r="B30" s="21"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="21"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
-      <c r="M30" s="21"/>
-      <c r="N30" s="21"/>
+    <row r="30" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="20"/>
+      <c r="N30" s="20"/>
     </row>
     <row r="31" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
     <row r="32" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="15">
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="22">
         <v>1</v>
       </c>
-      <c r="E32" s="15">
+      <c r="E32" s="22">
         <v>2</v>
       </c>
-      <c r="F32" s="15">
+      <c r="F32" s="22">
         <v>3</v>
       </c>
-      <c r="G32" s="15">
+      <c r="G32" s="22">
         <v>4</v>
       </c>
-      <c r="H32" s="15">
+      <c r="H32" s="22">
         <v>5</v>
       </c>
-      <c r="I32" s="15">
+      <c r="I32" s="22">
         <v>6</v>
       </c>
-      <c r="J32" s="15">
+      <c r="J32" s="22">
         <v>7</v>
       </c>
-      <c r="K32" s="15" t="s">
+      <c r="K32" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="L32" s="15" t="s">
+      <c r="L32" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="M32" s="15" t="s">
+      <c r="M32" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="N32" s="15" t="s">
+      <c r="N32" s="22" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="16" t="s">
+      <c r="A33" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="18"/>
-      <c r="J33" s="18"/>
-      <c r="K33" s="18"/>
-      <c r="L33" s="18"/>
-      <c r="M33" s="18"/>
-      <c r="N33" s="18"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="23"/>
+      <c r="K33" s="23"/>
+      <c r="L33" s="23"/>
+      <c r="M33" s="23"/>
+      <c r="N33" s="23"/>
     </row>
     <row r="34" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="18"/>
-      <c r="K34" s="18"/>
-      <c r="L34" s="18"/>
-      <c r="M34" s="18"/>
-      <c r="N34" s="18"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="23"/>
+      <c r="J34" s="23"/>
+      <c r="K34" s="23"/>
+      <c r="L34" s="23"/>
+      <c r="M34" s="23"/>
+      <c r="N34" s="23"/>
     </row>
     <row r="35" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="18"/>
-      <c r="K35" s="18"/>
-      <c r="L35" s="18"/>
-      <c r="M35" s="18"/>
-      <c r="N35" s="18"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="23"/>
+      <c r="I35" s="23"/>
+      <c r="J35" s="23"/>
+      <c r="K35" s="23"/>
+      <c r="L35" s="23"/>
+      <c r="M35" s="23"/>
+      <c r="N35" s="23"/>
     </row>
     <row r="36" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="18"/>
-      <c r="I36" s="18"/>
-      <c r="J36" s="18"/>
-      <c r="K36" s="18"/>
-      <c r="L36" s="18"/>
-      <c r="M36" s="18"/>
-      <c r="N36" s="18"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+      <c r="H36" s="23"/>
+      <c r="I36" s="23"/>
+      <c r="J36" s="23"/>
+      <c r="K36" s="23"/>
+      <c r="L36" s="23"/>
+      <c r="M36" s="23"/>
+      <c r="N36" s="23"/>
     </row>
     <row r="37" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
     <row r="38" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A38" s="13" t="s">
+      <c r="A38" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14"/>
-      <c r="K38" s="14"/>
-      <c r="L38" s="14"/>
-      <c r="M38" s="14"/>
-      <c r="N38" s="14"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="12"/>
+      <c r="K38" s="12"/>
+      <c r="L38" s="12"/>
+      <c r="M38" s="12"/>
+      <c r="N38" s="12"/>
     </row>
-    <row r="39" spans="1:14" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A39" s="19"/>
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19"/>
-      <c r="K39" s="19"/>
-      <c r="L39" s="19"/>
-      <c r="M39" s="19"/>
-      <c r="N39" s="19"/>
+    <row r="39" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="38"/>
+      <c r="B39" s="38"/>
+      <c r="C39" s="38"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="38"/>
+      <c r="G39" s="38"/>
+      <c r="H39" s="38"/>
+      <c r="I39" s="38"/>
+      <c r="J39" s="38"/>
+      <c r="K39" s="38"/>
+      <c r="L39" s="38"/>
+      <c r="M39" s="38"/>
+      <c r="N39" s="38"/>
     </row>
-    <row r="40" spans="1:14" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A40" s="19"/>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19"/>
-      <c r="K40" s="19"/>
-      <c r="L40" s="19"/>
-      <c r="M40" s="19"/>
-      <c r="N40" s="19"/>
+    <row r="40" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="24"/>
+      <c r="B40" s="24"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="24"/>
+      <c r="J40" s="24"/>
+      <c r="K40" s="24"/>
+      <c r="L40" s="24"/>
+      <c r="M40" s="24"/>
+      <c r="N40" s="24"/>
     </row>
-    <row r="41" spans="1:14" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A41" s="19"/>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
-      <c r="K41" s="19"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="19"/>
-      <c r="N41" s="19"/>
+    <row r="41" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="24"/>
+      <c r="B41" s="24"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
+      <c r="H41" s="24"/>
+      <c r="I41" s="24"/>
+      <c r="J41" s="24"/>
+      <c r="K41" s="24"/>
+      <c r="L41" s="24"/>
+      <c r="M41" s="24"/>
+      <c r="N41" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="F4"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G4"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="K4"/>
+    <mergeCell ref="C4:D4"/>
     <mergeCell ref="A1:N2"/>
     <mergeCell ref="A17:N17"/>
     <mergeCell ref="A36:C36"/>
@@ -3609,18 +3816,6 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="L10:N10"/>
-    <mergeCell ref="F4"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G4"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="K4"/>
-    <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.5" footer="0.5"/>
   <pageSetup scale="67" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/frontend/public/downloads/DiamondStats_Softball_Scorebook_Final.xlsx
+++ b/frontend/public/downloads/DiamondStats_Softball_Scorebook_Final.xlsx
@@ -228,7 +228,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -278,21 +278,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="dashDotDot">
-        <color indexed="64"/>
-      </left>
-      <right style="dashDotDot">
-        <color indexed="64"/>
-      </right>
-      <top style="dashDotDot">
-        <color indexed="64"/>
-      </top>
-      <bottom style="dashDotDot">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -329,110 +314,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="dashDotDot">
-        <color indexed="64"/>
-      </right>
-      <top style="dashDotDot">
-        <color indexed="64"/>
-      </top>
-      <bottom style="dashDotDot">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="dashDotDot">
-        <color indexed="64"/>
-      </right>
-      <top style="dashDotDot">
-        <color indexed="64"/>
-      </top>
-      <bottom style="dashDotDot">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashDotDot">
-        <color indexed="64"/>
-      </left>
-      <right style="dashDotDot">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="dashDotDot">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashDotDot">
-        <color indexed="64"/>
-      </left>
-      <right style="dashDotDot">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="dashDotDot">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashDotDot">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="dashDotDot">
-        <color indexed="64"/>
-      </top>
-      <bottom style="dashDotDot">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="dashDotDot">
-        <color indexed="64"/>
-      </top>
-      <bottom style="dashDotDot">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashDotDot">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="dashDotDot">
-        <color indexed="64"/>
-      </top>
-      <bottom style="dashDotDot">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -440,6 +326,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -463,6 +359,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -474,48 +371,23 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3107,63 +2979,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
     </row>
     <row r="2" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
     </row>
     <row r="3" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
     <row r="4" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="26" t="s">
+      <c r="B4" s="22"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="34"/>
-      <c r="G4" s="28" t="s">
+      <c r="F4" s="18"/>
+      <c r="G4" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="30"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="16" t="s">
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="29"/>
-      <c r="M4" s="27"/>
-      <c r="N4" s="27"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
     </row>
     <row r="5" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A5" s="2"/>
@@ -3182,46 +3054,46 @@
       <c r="N5" s="2"/>
     </row>
     <row r="6" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="16" t="s">
+      <c r="B6" s="28"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="17"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="27"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
     </row>
     <row r="8" spans="1:14" ht="26.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="K8" s="14" t="s">
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="K8" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
     </row>
     <row r="9" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="23" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -3230,154 +3102,154 @@
       <c r="C9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="23" t="s">
         <v>12</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="23" t="s">
         <v>14</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="18" t="s">
+      <c r="H9" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="I9" s="23" t="s">
         <v>44</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="13" t="s">
+      <c r="L9" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="32"/>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
       <c r="K10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L10" s="13" t="s">
+      <c r="L10" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
       <c r="K11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="L11" s="13" t="s">
+      <c r="L11" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
       <c r="K12" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="L12" s="13" t="s">
+      <c r="L12" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
       <c r="K13" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="L13" s="13" t="s">
+      <c r="L13" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
       <c r="K14" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="L14" s="13" t="s">
+      <c r="L14" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
     </row>
     <row r="17" spans="1:14" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
     </row>
     <row r="18" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A18" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="23" t="s">
         <v>29</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -3386,10 +3258,10 @@
       <c r="E18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="F18" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="18" t="s">
+      <c r="G18" s="23" t="s">
         <v>33</v>
       </c>
       <c r="H18" s="3" t="s">
@@ -3398,13 +3270,13 @@
       <c r="I18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="J18" s="18" t="s">
+      <c r="J18" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="K18" s="18" t="s">
+      <c r="K18" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="L18" s="18" t="s">
+      <c r="L18" s="23" t="s">
         <v>14</v>
       </c>
       <c r="M18" s="3" t="s">
@@ -3414,377 +3286,377 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="31"/>
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="32"/>
-      <c r="L19" s="32"/>
-      <c r="M19" s="31"/>
-      <c r="N19" s="31"/>
+    <row r="19" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
     </row>
-    <row r="20" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="20"/>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-      <c r="M20" s="20"/>
-      <c r="N20" s="20"/>
+    <row r="20" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
     </row>
-    <row r="21" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
+    <row r="21" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
     </row>
-    <row r="22" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="20"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
+    <row r="22" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
     </row>
-    <row r="23" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
+    <row r="23" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
     </row>
-    <row r="24" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="20"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
+    <row r="24" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
     </row>
-    <row r="25" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
+    <row r="25" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
     </row>
-    <row r="26" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="20"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="20"/>
-      <c r="N26" s="20"/>
+    <row r="26" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
     </row>
-    <row r="27" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="19"/>
+    <row r="27" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
     </row>
-    <row r="28" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="20"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
-      <c r="N28" s="20"/>
+    <row r="28" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
     </row>
-    <row r="29" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="19"/>
+    <row r="29" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
     </row>
-    <row r="30" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="20"/>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
-      <c r="M30" s="20"/>
-      <c r="N30" s="20"/>
+    <row r="30" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
     </row>
     <row r="31" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
     <row r="32" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="22">
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="25">
         <v>1</v>
       </c>
-      <c r="E32" s="22">
+      <c r="E32" s="25">
         <v>2</v>
       </c>
-      <c r="F32" s="22">
+      <c r="F32" s="25">
         <v>3</v>
       </c>
-      <c r="G32" s="22">
+      <c r="G32" s="25">
         <v>4</v>
       </c>
-      <c r="H32" s="22">
+      <c r="H32" s="25">
         <v>5</v>
       </c>
-      <c r="I32" s="22">
+      <c r="I32" s="25">
         <v>6</v>
       </c>
-      <c r="J32" s="22">
+      <c r="J32" s="25">
         <v>7</v>
       </c>
-      <c r="K32" s="22" t="s">
+      <c r="K32" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="L32" s="22" t="s">
+      <c r="L32" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="M32" s="22" t="s">
+      <c r="M32" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="N32" s="22" t="s">
+      <c r="N32" s="25" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="10"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="23"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="23"/>
-      <c r="L33" s="23"/>
-      <c r="M33" s="23"/>
-      <c r="N33" s="23"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
     </row>
     <row r="34" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A34" s="9" t="s">
+      <c r="A34" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="21"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="23"/>
-      <c r="J34" s="23"/>
-      <c r="K34" s="23"/>
-      <c r="L34" s="23"/>
-      <c r="M34" s="23"/>
-      <c r="N34" s="23"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
     </row>
     <row r="35" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="23"/>
-      <c r="H35" s="23"/>
-      <c r="I35" s="23"/>
-      <c r="J35" s="23"/>
-      <c r="K35" s="23"/>
-      <c r="L35" s="23"/>
-      <c r="M35" s="23"/>
-      <c r="N35" s="23"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
     </row>
     <row r="36" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A36" s="9" t="s">
+      <c r="A36" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="10"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="36"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="23"/>
-      <c r="I36" s="23"/>
-      <c r="J36" s="23"/>
-      <c r="K36" s="23"/>
-      <c r="L36" s="23"/>
-      <c r="M36" s="23"/>
-      <c r="N36" s="23"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
     </row>
     <row r="37" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
     <row r="38" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A38" s="11" t="s">
+      <c r="A38" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="12"/>
-      <c r="J38" s="12"/>
-      <c r="K38" s="12"/>
-      <c r="L38" s="12"/>
-      <c r="M38" s="12"/>
-      <c r="N38" s="12"/>
+      <c r="B38" s="27"/>
+      <c r="C38" s="27"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="27"/>
+      <c r="I38" s="27"/>
+      <c r="J38" s="27"/>
+      <c r="K38" s="27"/>
+      <c r="L38" s="27"/>
+      <c r="M38" s="27"/>
+      <c r="N38" s="27"/>
     </row>
-    <row r="39" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="38"/>
-      <c r="B39" s="38"/>
-      <c r="C39" s="38"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="38"/>
-      <c r="F39" s="38"/>
-      <c r="G39" s="38"/>
-      <c r="H39" s="38"/>
-      <c r="I39" s="38"/>
-      <c r="J39" s="38"/>
-      <c r="K39" s="38"/>
-      <c r="L39" s="38"/>
-      <c r="M39" s="38"/>
-      <c r="N39" s="38"/>
+    <row r="39" spans="1:14" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="6"/>
     </row>
-    <row r="40" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="24"/>
-      <c r="B40" s="24"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="24"/>
-      <c r="I40" s="24"/>
-      <c r="J40" s="24"/>
-      <c r="K40" s="24"/>
-      <c r="L40" s="24"/>
-      <c r="M40" s="24"/>
-      <c r="N40" s="24"/>
+    <row r="40" spans="1:14" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="6"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="6"/>
     </row>
-    <row r="41" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="24"/>
-      <c r="B41" s="24"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="24"/>
-      <c r="I41" s="24"/>
-      <c r="J41" s="24"/>
-      <c r="K41" s="24"/>
-      <c r="L41" s="24"/>
-      <c r="M41" s="24"/>
-      <c r="N41" s="24"/>
+    <row r="41" spans="1:14" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="6"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="28">

--- a/frontend/public/downloads/DiamondStats_Softball_Scorebook_Final.xlsx
+++ b/frontend/public/downloads/DiamondStats_Softball_Scorebook_Final.xlsx
@@ -318,7 +318,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -338,20 +338,13 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -359,17 +352,27 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -377,16 +380,19 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2979,63 +2985,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
     </row>
     <row r="2" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
     </row>
     <row r="3" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
     <row r="4" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="29" t="s">
+      <c r="B4" s="18"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="18"/>
-      <c r="G4" s="30" t="s">
+      <c r="F4" s="11"/>
+      <c r="G4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="21" t="s">
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
     </row>
     <row r="5" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A5" s="2"/>
@@ -3054,46 +3060,46 @@
       <c r="N5" s="2"/>
     </row>
     <row r="6" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="21" t="s">
+      <c r="B6" s="20"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="22"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
     </row>
     <row r="8" spans="1:14" ht="26.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="K8" s="19" t="s">
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="K8" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="20"/>
-      <c r="M8" s="20"/>
-      <c r="N8" s="20"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="29"/>
     </row>
     <row r="9" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -3102,35 +3108,37 @@
       <c r="C9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="9" t="s">
         <v>12</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F9" s="9" t="s">
         <v>14</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="23" t="s">
+      <c r="H9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="23" t="s">
+      <c r="I9" s="9" t="s">
         <v>44</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="17" t="s">
+      <c r="L9" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
     </row>
     <row r="10" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="7"/>
+      <c r="A10" s="31">
+        <v>1</v>
+      </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -3142,14 +3150,16 @@
       <c r="K10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L10" s="17" t="s">
+      <c r="L10" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
     </row>
     <row r="11" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="7"/>
+      <c r="A11" s="31">
+        <v>2</v>
+      </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -3161,14 +3171,16 @@
       <c r="K11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="L11" s="17" t="s">
+      <c r="L11" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
     </row>
     <row r="12" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="7"/>
+      <c r="A12" s="31">
+        <v>3</v>
+      </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -3180,14 +3192,16 @@
       <c r="K12" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="L12" s="17" t="s">
+      <c r="L12" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
     </row>
     <row r="13" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="7"/>
+      <c r="A13" s="31">
+        <v>4</v>
+      </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -3199,14 +3213,16 @@
       <c r="K13" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="L13" s="17" t="s">
+      <c r="L13" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
     </row>
     <row r="14" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="7"/>
+      <c r="A14" s="31">
+        <v>5</v>
+      </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -3218,38 +3234,38 @@
       <c r="K14" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="L14" s="17" t="s">
+      <c r="L14" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
     </row>
     <row r="17" spans="1:14" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16"/>
     </row>
     <row r="18" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A18" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="9" t="s">
         <v>29</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -3258,10 +3274,10 @@
       <c r="E18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="23" t="s">
+      <c r="F18" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="23" t="s">
+      <c r="G18" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H18" s="3" t="s">
@@ -3270,13 +3286,13 @@
       <c r="I18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="J18" s="23" t="s">
+      <c r="J18" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="K18" s="23" t="s">
+      <c r="K18" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L18" s="23" t="s">
+      <c r="L18" s="9" t="s">
         <v>14</v>
       </c>
       <c r="M18" s="3" t="s">
@@ -3287,7 +3303,9 @@
       </c>
     </row>
     <row r="19" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A19" s="7"/>
+      <c r="A19" s="31">
+        <v>1</v>
+      </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
@@ -3303,7 +3321,9 @@
       <c r="N19" s="7"/>
     </row>
     <row r="20" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A20" s="8"/>
+      <c r="A20" s="32">
+        <v>2</v>
+      </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
@@ -3319,7 +3339,9 @@
       <c r="N20" s="8"/>
     </row>
     <row r="21" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A21" s="7"/>
+      <c r="A21" s="31">
+        <v>3</v>
+      </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
@@ -3335,7 +3357,9 @@
       <c r="N21" s="7"/>
     </row>
     <row r="22" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="8"/>
+      <c r="A22" s="32">
+        <v>4</v>
+      </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
@@ -3351,7 +3375,9 @@
       <c r="N22" s="8"/>
     </row>
     <row r="23" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A23" s="7"/>
+      <c r="A23" s="31">
+        <v>5</v>
+      </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
@@ -3367,7 +3393,9 @@
       <c r="N23" s="7"/>
     </row>
     <row r="24" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A24" s="8"/>
+      <c r="A24" s="32">
+        <v>6</v>
+      </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
@@ -3383,7 +3411,9 @@
       <c r="N24" s="8"/>
     </row>
     <row r="25" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A25" s="7"/>
+      <c r="A25" s="31">
+        <v>7</v>
+      </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
@@ -3399,7 +3429,9 @@
       <c r="N25" s="7"/>
     </row>
     <row r="26" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A26" s="8"/>
+      <c r="A26" s="32">
+        <v>8</v>
+      </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
@@ -3415,7 +3447,9 @@
       <c r="N26" s="8"/>
     </row>
     <row r="27" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A27" s="7"/>
+      <c r="A27" s="31">
+        <v>9</v>
+      </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
@@ -3431,7 +3465,9 @@
       <c r="N27" s="7"/>
     </row>
     <row r="28" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A28" s="8"/>
+      <c r="A28" s="32">
+        <v>10</v>
+      </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
@@ -3447,7 +3483,9 @@
       <c r="N28" s="8"/>
     </row>
     <row r="29" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A29" s="7"/>
+      <c r="A29" s="31">
+        <v>11</v>
+      </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -3463,7 +3501,9 @@
       <c r="N29" s="7"/>
     </row>
     <row r="30" spans="1:14" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A30" s="8"/>
+      <c r="A30" s="32">
+        <v>12</v>
+      </c>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -3480,51 +3520,51 @@
     </row>
     <row r="31" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
     <row r="32" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="25">
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="10">
         <v>1</v>
       </c>
-      <c r="E32" s="25">
+      <c r="E32" s="10">
         <v>2</v>
       </c>
-      <c r="F32" s="25">
+      <c r="F32" s="10">
         <v>3</v>
       </c>
-      <c r="G32" s="25">
+      <c r="G32" s="10">
         <v>4</v>
       </c>
-      <c r="H32" s="25">
+      <c r="H32" s="10">
         <v>5</v>
       </c>
-      <c r="I32" s="25">
+      <c r="I32" s="10">
         <v>6</v>
       </c>
-      <c r="J32" s="25">
+      <c r="J32" s="10">
         <v>7</v>
       </c>
-      <c r="K32" s="25" t="s">
+      <c r="K32" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="L32" s="25" t="s">
+      <c r="L32" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="M32" s="25" t="s">
+      <c r="M32" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="N32" s="25" t="s">
+      <c r="N32" s="10" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="13" t="s">
+      <c r="A33" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="24"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="25"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
@@ -3538,11 +3578,11 @@
       <c r="N33" s="5"/>
     </row>
     <row r="34" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A34" s="13" t="s">
+      <c r="A34" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="24"/>
+      <c r="B34" s="24"/>
+      <c r="C34" s="25"/>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
@@ -3556,11 +3596,11 @@
       <c r="N34" s="5"/>
     </row>
     <row r="35" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A35" s="13" t="s">
+      <c r="A35" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="24"/>
+      <c r="B35" s="24"/>
+      <c r="C35" s="25"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
@@ -3574,11 +3614,11 @@
       <c r="N35" s="5"/>
     </row>
     <row r="36" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A36" s="13" t="s">
+      <c r="A36" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="24"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="25"/>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
@@ -3660,18 +3700,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="F4"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G4"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="K4"/>
-    <mergeCell ref="C4:D4"/>
     <mergeCell ref="A1:N2"/>
     <mergeCell ref="A17:N17"/>
     <mergeCell ref="A36:C36"/>
@@ -3688,6 +3716,18 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="L10:N10"/>
+    <mergeCell ref="F4"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G4"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="K4"/>
+    <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.5" footer="0.5"/>
   <pageSetup scale="67" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
